--- a/prospecting/50k-collected-multichannel-model.xlsx
+++ b/prospecting/50k-collected-multichannel-model.xlsx
@@ -12,6 +12,8 @@
     <sheet name="Paid Ads" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Up-Market Pricing" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Timeline" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Industry Profiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Strategy Compare" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,8 +25,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;(#,##0.0);-"/>
-    <numFmt numFmtId="166" formatCode="0.0%;(0.0%);-"/>
-    <numFmt numFmtId="167" formatCode="#,##0;(#,##0);-"/>
+    <numFmt numFmtId="166" formatCode="#,##0;(#,##0);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%;(0.0%);-"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -134,7 +136,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -156,11 +158,44 @@
         <color rgb="00B7C2C6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B7C2C6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7C2C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7C2C6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7C2C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7C2C6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7C2C6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,18 +210,18 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,7 +233,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,6 +262,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -317,27 +371,28 @@
 This costs you a full month versus an exit-run-rate target.</t>
       </text>
     </comment>
-    <comment ref="C32" authorId="0" shapeId="0">
+    <comment ref="C38" authorId="0" shapeId="0">
       <text>
         <t>Model uses 20% because the signal matrix filters FOR mobile-reachable owners.</t>
       </text>
     </comment>
-    <comment ref="C33" authorId="0" shapeId="0">
+    <comment ref="C39" authorId="0" shapeId="0">
       <text>
         <t>RISKIEST ASSUMPTION. Near top quartile. Unproven until the pilot.</t>
       </text>
     </comment>
-    <comment ref="C34" authorId="0" shapeId="0">
+    <comment ref="C40" authorId="0" shapeId="0">
       <text>
         <t>A guess. Measure it.</t>
       </text>
     </comment>
-    <comment ref="C35" authorId="0" shapeId="0">
+    <comment ref="C41" authorId="0" shapeId="0">
       <text>
-        <t>At $48K ACV you sit in the 20-28% band. 25% is mid-band.</t>
+        <t>Barbell blends a mid-market band (20-28%) with a faster fast-tier.
+27% assumes the fast tier closes near the top of its band.</t>
       </text>
     </comment>
-    <comment ref="C39" authorId="0" shapeId="0">
+    <comment ref="C45" authorId="0" shapeId="0">
       <text>
         <t>B2B Meta CPL averages $63.40; qualified B2B leads $150-250.
 Your account shows $1.21 CPL, but that came from a DIFFERENT
@@ -639,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F52"/>
+  <dimension ref="B2:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -754,484 +809,553 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>DEAL ECONOMICS — UP-MARKET</t>
+          <t>DEAL ECONOMICS — BARBELL: two segments</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Group tier carries the revenue. Fast tier de-risks the 30 Nov deadline with a shorter cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Source / note</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Blended ACV per month</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Recommended. Mid-market agencies charge $5-15K; multi-location SEO alone is $3-6K.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Annualised contract value</t>
-        </is>
-      </c>
-      <c r="C17" s="12">
-        <f>C16*12</f>
-        <v/>
+          <t>GROUP tier — customers</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>5</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Determines the win-rate band and cycle length.</t>
+          <t>3-8 location med spa groups. 30-90 day cycle.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>0.65</v>
+          <t>GROUP tier — ACV per month</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Below the mid-market agency floor of $5,000 with more scope.</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Total customers required</t>
-        </is>
-      </c>
-      <c r="C19" s="14">
-        <f>IF(C16&lt;=0,0,ROUNDUP(C11/C16,0))</f>
-        <v/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>FAST tier — customers</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Single-location HVAC, plumbing LEADERS only, med spa $1.5M+. 14-45 day cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>FAST tier — ACV per month</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Month-to-month, one decision maker, runs in their existing stack.</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>CHANNEL MIX — how the customers are sourced</t>
-        </is>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Total customers</t>
+        </is>
+      </c>
+      <c r="C21" s="13">
+        <f>C17+C19</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>New MRR from both tiers</t>
+        </is>
+      </c>
+      <c r="C22" s="9">
+        <f>C17*C18+C19*C20</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>From outbound</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Proven, controllable motion. Does not depend on unvalidated CPL.</t>
-        </is>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Blended ACV per month</t>
+        </is>
+      </c>
+      <c r="C23" s="14">
+        <f>IF(C21&lt;=0,0,C22/C21)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>From paid ads</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="C24" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Real upside, sub-month payback, but only $303 of history. Gate the spend.</t>
-        </is>
+        <v>0.65</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>From referral / existing base</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Cheapest revenue available and currently unassigned to anyone.</t>
-        </is>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Covers the gap?</t>
+        </is>
+      </c>
+      <c r="C25" s="16">
+        <f>IF(C22&gt;=C11,"YES","SHORT")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Total planned</t>
-        </is>
-      </c>
-      <c r="C26" s="16">
-        <f>SUM(C23:C25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Check vs required</t>
-        </is>
-      </c>
-      <c r="C27" s="17">
-        <f>IF(C26&gt;=C19,"COVERED","SHORT")</f>
+          <t>Projected December collected</t>
+        </is>
+      </c>
+      <c r="C26" s="9">
+        <f>C10+C22</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Projected December collected</t>
-        </is>
-      </c>
-      <c r="C28" s="9">
-        <f>C10+C26*C16</f>
-        <v/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>CHANNEL MIX — how the customers are sourced</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>OUTBOUND CONVERSION RATES</t>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>From outbound</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Proven, controllable. Does not depend on unvalidated CPL.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Bench avg</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Top qtile</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>From paid ads</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Real upside, sub-month payback, but only $303 of history. Gate the spend.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
+          <t>From referral / existing base</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Cheapest revenue available and currently unassigned to anyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Total sourced</t>
+        </is>
+      </c>
+      <c r="C33" s="17">
+        <f>SUM(C30:C32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Matches total customers?</t>
+        </is>
+      </c>
+      <c r="C34" s="16">
+        <f>IF(C33&gt;=C21,"COVERED","SHORT")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>OUTBOUND CONVERSION RATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Bench avg</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Top qtile</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>Dial to live connect</t>
         </is>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C38" s="15" t="n">
         <v>0.2</v>
       </c>
-      <c r="D32" s="18" t="n">
+      <c r="D38" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="E32" s="18" t="n">
+      <c r="E38" s="18" t="n">
         <v>0.22</v>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>Generic data 8-12%; verified mobile direct-dial 18-22%. Gong avg 5.4%, top qtile 13.3%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Connect to meeting (set rate)</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Gong 300M+ calls: avg 4.6%, top quartile 16.7%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Meeting to qualified opp</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Not benchmarked. Signal-qualified should beat generic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Qualified opp to close</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>$10-50K ACV band: 20-28%. Above 40% sustained means underpriced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>PAID ADS</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>Source / note</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Cost per lead</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>125</v>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>B2B avg $63.40; qualified $150-250. Your $1.21 was a different offer with instant forms.</t>
+          <t>Connect to meeting (set rate)</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Gong 300M+ calls: avg 4.6%, top quartile 16.7%.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Lead to customer conversion</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="n">
-        <v>0.05</v>
+          <t>Meeting to qualified opp</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>0.7</v>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Professional services 4.6% (highest B2B category). Inbound 5-10%, outbound 1-3%.</t>
+          <t>Not benchmarked. Signal-qualified should beat generic.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Implied CAC from ads</t>
-        </is>
-      </c>
-      <c r="C41" s="12">
-        <f>IF(C40&lt;=0,0,C39/C40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Payback in months of ACV</t>
-        </is>
-      </c>
-      <c r="C42" s="19">
-        <f>IF(C16&lt;=0,0,C41/C16)</f>
-        <v/>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Qualified opp to close</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>$10-50K ACV: 20-28%. Sub-$10K: 28-35%. Above 40% sustained means underpriced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>PAID ADS</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>CADENCE AND CAPACITY</t>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Source / note</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Source / note</t>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Cost per lead</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>B2B avg $63.40; qualified $150-250. Your $1.21 was a different offer with instant forms.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Emails per prospect</t>
+          <t>Lead to customer conversion</t>
         </is>
       </c>
       <c r="C46" s="15" t="n">
-        <v>3</v>
+        <v>0.05</v>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Sweet spot is 3-4. Total cadence 8-12 touches across channels.</t>
+          <t>Professional services 4.6% (highest B2B category). Inbound 5-10%, outbound 1-3%.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Written consent rate, per connect</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>Share of live conversations that produce a written SMS opt-in. Unmeasured.</t>
-        </is>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Implied CAC from ads</t>
+        </is>
+      </c>
+      <c r="C47" s="14">
+        <f>IF(C46&lt;=0,0,C45/C46)</f>
+        <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>SMS per consented prospect</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Number of callers</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="n">
-        <v>2</v>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Payback in months of ACV</t>
+        </is>
+      </c>
+      <c r="C48" s="19">
+        <f>IF(C23&lt;=0,0,C47/C23)</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Selling days per month</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="n">
-        <v>20</v>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>CADENCE AND CAPACITY</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Sustainable dials per person per day</t>
-        </is>
-      </c>
-      <c r="C51" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Ceiling for someone who also closes and delivers. A full-time dialer does 80-100.</t>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Source / note</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
+          <t>Emails per prospect</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Sweet spot is 3-4. Total cadence 8-12 touches across channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Written consent rate, per connect</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Share of live conversations that produce a written SMS opt-in. Unmeasured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>SMS per consented prospect</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Number of callers</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Selling days per month</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Sustainable dials per person per day</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Ceiling for someone who also closes and delivers. A full-time dialer does 80-100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
           <t>Gmail bulk-sender line, per day</t>
         </is>
       </c>
-      <c r="C52" s="20" t="n">
+      <c r="C58" s="20" t="n">
         <v>5000</v>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>Crossing this classifies the domain as a bulk sender PERMANENTLY. Never approach it.</t>
         </is>
@@ -1315,11 +1439,11 @@
         </is>
       </c>
       <c r="C7" s="19">
-        <f>IF(Assumptions!C12&lt;=0,0,Assumptions!C23/Assumptions!C12)</f>
+        <f>IF(Assumptions!C12&lt;=0,0,Assumptions!C30/Assumptions!C12)</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>Assumptions!C23</f>
+        <f>Assumptions!C30</f>
         <v/>
       </c>
     </row>
@@ -1330,15 +1454,15 @@
         </is>
       </c>
       <c r="C8" s="22">
-        <f>IF(Assumptions!C35&lt;=0,0,C7/Assumptions!C35)</f>
-        <v/>
-      </c>
-      <c r="D8" s="16">
+        <f>IF(Assumptions!C41&lt;=0,0,C7/Assumptions!C41)</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
         <f>C8*Assumptions!C12</f>
         <v/>
       </c>
       <c r="E8" s="23">
-        <f>Assumptions!C35</f>
+        <f>Assumptions!C41</f>
         <v/>
       </c>
     </row>
@@ -1349,15 +1473,15 @@
         </is>
       </c>
       <c r="C9" s="22">
-        <f>IF(Assumptions!C34&lt;=0,0,C8/Assumptions!C34)</f>
-        <v/>
-      </c>
-      <c r="D9" s="16">
+        <f>IF(Assumptions!C40&lt;=0,0,C8/Assumptions!C40)</f>
+        <v/>
+      </c>
+      <c r="D9" s="17">
         <f>C9*Assumptions!C12</f>
         <v/>
       </c>
       <c r="E9" s="23">
-        <f>Assumptions!C34</f>
+        <f>Assumptions!C40</f>
         <v/>
       </c>
     </row>
@@ -1367,16 +1491,16 @@
           <t>Live connects</t>
         </is>
       </c>
-      <c r="C10" s="16">
-        <f>IF(Assumptions!C33&lt;=0,0,C9/Assumptions!C33)</f>
-        <v/>
-      </c>
-      <c r="D10" s="16">
+      <c r="C10" s="17">
+        <f>IF(Assumptions!C39&lt;=0,0,C9/Assumptions!C39)</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
         <f>C10*Assumptions!C12</f>
         <v/>
       </c>
       <c r="E10" s="23">
-        <f>Assumptions!C33</f>
+        <f>Assumptions!C39</f>
         <v/>
       </c>
     </row>
@@ -1386,16 +1510,16 @@
           <t>DIALS REQUIRED</t>
         </is>
       </c>
-      <c r="C11" s="14">
-        <f>IF(Assumptions!C32&lt;=0,0,C10/Assumptions!C32)</f>
-        <v/>
-      </c>
-      <c r="D11" s="16">
+      <c r="C11" s="13">
+        <f>IF(Assumptions!C38&lt;=0,0,C10/Assumptions!C38)</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
         <f>C11*Assumptions!C12</f>
         <v/>
       </c>
       <c r="E11" s="23">
-        <f>Assumptions!C32</f>
+        <f>Assumptions!C38</f>
         <v/>
       </c>
     </row>
@@ -1439,19 +1563,19 @@
           <t>Dials</t>
         </is>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="17">
         <f>C11</f>
         <v/>
       </c>
-      <c r="D15" s="16">
-        <f>IF(Assumptions!C50&lt;=0,0,C15/Assumptions!C50)</f>
+      <c r="D15" s="17">
+        <f>IF(Assumptions!C56&lt;=0,0,C15/Assumptions!C56)</f>
         <v/>
       </c>
       <c r="E15" s="21">
-        <f>Assumptions!C51*Assumptions!C49</f>
-        <v/>
-      </c>
-      <c r="F15" s="17">
+        <f>Assumptions!C57*Assumptions!C55</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
         <f>IF(D15&lt;=E15,"OK","OVER CAPACITY")</f>
         <v/>
       </c>
@@ -1463,12 +1587,12 @@
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr"/>
-      <c r="D16" s="16">
-        <f>IF(Assumptions!C49&lt;=0,0,D15/Assumptions!C49)</f>
+      <c r="D16" s="17">
+        <f>IF(Assumptions!C55&lt;=0,0,D15/Assumptions!C55)</f>
         <v/>
       </c>
       <c r="E16" s="21">
-        <f>Assumptions!C51</f>
+        <f>Assumptions!C57</f>
         <v/>
       </c>
       <c r="F16" s="25">
@@ -1482,19 +1606,19 @@
           <t>Emails</t>
         </is>
       </c>
-      <c r="C17" s="16">
-        <f>C11*Assumptions!C46</f>
-        <v/>
-      </c>
-      <c r="D17" s="16">
-        <f>IF(Assumptions!C50&lt;=0,0,C17/Assumptions!C50)</f>
+      <c r="C17" s="17">
+        <f>C11*Assumptions!C52</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>IF(Assumptions!C56&lt;=0,0,C17/Assumptions!C56)</f>
         <v/>
       </c>
       <c r="E17" s="21">
-        <f>Assumptions!C52</f>
-        <v/>
-      </c>
-      <c r="F17" s="17">
+        <f>Assumptions!C58</f>
+        <v/>
+      </c>
+      <c r="F17" s="16">
         <f>IF(D17&lt;=E17,"OK","BULK SENDER RISK")</f>
         <v/>
       </c>
@@ -1505,8 +1629,8 @@
           <t>Consented prospects</t>
         </is>
       </c>
-      <c r="C18" s="16">
-        <f>C10*Assumptions!C47</f>
+      <c r="C18" s="17">
+        <f>C10*Assumptions!C53</f>
         <v/>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -1521,12 +1645,12 @@
           <t>SMS</t>
         </is>
       </c>
-      <c r="C19" s="16">
-        <f>C18*Assumptions!C48</f>
-        <v/>
-      </c>
-      <c r="D19" s="16">
-        <f>IF(Assumptions!C50&lt;=0,0,C19/Assumptions!C50)</f>
+      <c r="C19" s="17">
+        <f>C18*Assumptions!C54</f>
+        <v/>
+      </c>
+      <c r="D19" s="17">
+        <f>IF(Assumptions!C56&lt;=0,0,C19/Assumptions!C56)</f>
         <v/>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -1575,14 +1699,14 @@
           <t>Email replies</t>
         </is>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="17">
         <f>C17</f>
         <v/>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="15" t="n">
         <v>0.0343</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="17">
         <f>C23*D23</f>
         <v/>
       </c>
@@ -1598,14 +1722,14 @@
           <t>SMS responses</t>
         </is>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="17">
         <f>C19</f>
         <v/>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="15" t="n">
         <v>0.45</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <f>C24*D24</f>
         <v/>
       </c>
@@ -1905,15 +2029,15 @@
       <c r="C21" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="15" t="n">
         <v>0.03</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="14">
         <f>IF(D21&lt;=0,0,C21/D21)</f>
         <v/>
       </c>
       <c r="F21" s="22">
-        <f>IF(Assumptions!$C$16&lt;=0,0,E21/Assumptions!$C$16)</f>
+        <f>IF(Assumptions!$C$23&lt;=0,0,E21/Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
@@ -1926,7 +2050,7 @@
       <c r="C22" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="E22" s="9">
@@ -1934,7 +2058,7 @@
         <v/>
       </c>
       <c r="F22" s="19">
-        <f>IF(Assumptions!$C$16&lt;=0,0,E22/Assumptions!$C$16)</f>
+        <f>IF(Assumptions!$C$23&lt;=0,0,E22/Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
@@ -1947,15 +2071,15 @@
       <c r="C23" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="14">
         <f>IF(D23&lt;=0,0,C23/D23)</f>
         <v/>
       </c>
       <c r="F23" s="22">
-        <f>IF(Assumptions!$C$16&lt;=0,0,E23/Assumptions!$C$16)</f>
+        <f>IF(Assumptions!$C$23&lt;=0,0,E23/Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
@@ -1997,15 +2121,15 @@
       <c r="B27" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="16">
-        <f>IF(Assumptions!$C$40&lt;=0,0,B27/Assumptions!$C$40)</f>
-        <v/>
-      </c>
-      <c r="D27" s="12">
-        <f>C27*Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="E27" s="12">
+      <c r="C27" s="17">
+        <f>IF(Assumptions!$C$46&lt;=0,0,B27/Assumptions!$C$46)</f>
+        <v/>
+      </c>
+      <c r="D27" s="14">
+        <f>C27*Assumptions!$C$45</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
         <f>C27*200</f>
         <v/>
       </c>
@@ -2014,12 +2138,12 @@
       <c r="B28" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="14">
-        <f>IF(Assumptions!$C$40&lt;=0,0,B28/Assumptions!$C$40)</f>
+      <c r="C28" s="13">
+        <f>IF(Assumptions!$C$46&lt;=0,0,B28/Assumptions!$C$46)</f>
         <v/>
       </c>
       <c r="D28" s="9">
-        <f>C28*Assumptions!$C$39</f>
+        <f>C28*Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="E28" s="9">
@@ -2036,15 +2160,15 @@
       <c r="B29" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="16">
-        <f>IF(Assumptions!$C$40&lt;=0,0,B29/Assumptions!$C$40)</f>
-        <v/>
-      </c>
-      <c r="D29" s="12">
-        <f>C29*Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="E29" s="12">
+      <c r="C29" s="17">
+        <f>IF(Assumptions!$C$46&lt;=0,0,B29/Assumptions!$C$46)</f>
+        <v/>
+      </c>
+      <c r="D29" s="14">
+        <f>C29*Assumptions!$C$45</f>
+        <v/>
+      </c>
+      <c r="E29" s="14">
         <f>C29*200</f>
         <v/>
       </c>
@@ -2053,15 +2177,15 @@
       <c r="B30" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="C30" s="16">
-        <f>IF(Assumptions!$C$40&lt;=0,0,B30/Assumptions!$C$40)</f>
-        <v/>
-      </c>
-      <c r="D30" s="12">
-        <f>C30*Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="E30" s="12">
+      <c r="C30" s="17">
+        <f>IF(Assumptions!$C$46&lt;=0,0,B30/Assumptions!$C$46)</f>
+        <v/>
+      </c>
+      <c r="D30" s="14">
+        <f>C30*Assumptions!$C$45</f>
+        <v/>
+      </c>
+      <c r="E30" s="14">
         <f>C30*200</f>
         <v/>
       </c>
@@ -2070,15 +2194,15 @@
       <c r="B31" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="C31" s="16">
-        <f>IF(Assumptions!$C$40&lt;=0,0,B31/Assumptions!$C$40)</f>
-        <v/>
-      </c>
-      <c r="D31" s="12">
-        <f>C31*Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="E31" s="12">
+      <c r="C31" s="17">
+        <f>IF(Assumptions!$C$46&lt;=0,0,B31/Assumptions!$C$46)</f>
+        <v/>
+      </c>
+      <c r="D31" s="14">
+        <f>C31*Assumptions!$C$45</f>
+        <v/>
+      </c>
+      <c r="E31" s="14">
         <f>C31*200</f>
         <v/>
       </c>
@@ -2095,7 +2219,7 @@
         </is>
       </c>
       <c r="C33" s="9">
-        <f>IF(Assumptions!C40&lt;=0,0,Assumptions!C24/Assumptions!C40*Assumptions!C39)</f>
+        <f>IF(Assumptions!C46&lt;=0,0,Assumptions!C31/Assumptions!C46*Assumptions!C45)</f>
         <v/>
       </c>
     </row>
@@ -2530,8 +2654,8 @@
       <c r="D18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="E18" s="12">
-        <f>D18*12*Assumptions!$C$18</f>
+      <c r="E18" s="14">
+        <f>D18*12*Assumptions!$C$24</f>
         <v/>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -2555,7 +2679,7 @@
         <v>5000</v>
       </c>
       <c r="E19" s="9">
-        <f>D19*12*Assumptions!$C$18</f>
+        <f>D19*12*Assumptions!$C$24</f>
         <v/>
       </c>
       <c r="F19" s="33" t="inlineStr">
@@ -2578,8 +2702,8 @@
       <c r="D20" s="7" t="n">
         <v>8000</v>
       </c>
-      <c r="E20" s="12">
-        <f>D20*12*Assumptions!$C$18</f>
+      <c r="E20" s="14">
+        <f>D20*12*Assumptions!$C$24</f>
         <v/>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -2602,8 +2726,8 @@
       <c r="D21" s="7" t="n">
         <v>12000</v>
       </c>
-      <c r="E21" s="12">
-        <f>D21*12*Assumptions!$C$18</f>
+      <c r="E21" s="14">
+        <f>D21*12*Assumptions!$C$24</f>
         <v/>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2703,7 +2827,7 @@
       <c r="B29" s="37" t="n">
         <v>6000</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="14">
         <f>B29*12</f>
         <v/>
       </c>
@@ -3150,4 +3274,1000 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Industry Economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Every figure sourced. See 05-industry-icp-fast-market.md for citations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Med Spa</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Auto Detailing</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Typical revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>$750K-1.5M</t>
+        </is>
+      </c>
+      <c r="D6" s="58" t="inlineStr">
+        <is>
+          <t>$1.28M avg</t>
+        </is>
+      </c>
+      <c r="E6" s="58" t="inlineStr">
+        <is>
+          <t>$1.86M median</t>
+        </is>
+      </c>
+      <c r="F6" s="58" t="inlineStr">
+        <is>
+          <t>~$168K mobile</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Med spa leads by a wide margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="59" t="inlineStr">
+        <is>
+          <t>Average employees</t>
+        </is>
+      </c>
+      <c r="C7" s="60" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="D7" s="60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="60" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F7" s="60" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>All owner-operator scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Average ticket</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="inlineStr">
+        <is>
+          <t>$1,400-1,800</t>
+        </is>
+      </c>
+      <c r="D8" s="58" t="inlineStr">
+        <is>
+          <t>$150-500</t>
+        </is>
+      </c>
+      <c r="E8" s="58" t="inlineStr">
+        <is>
+          <t>$450-600/visit</t>
+        </is>
+      </c>
+      <c r="F8" s="58" t="inlineStr">
+        <is>
+          <t>$185</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Ticket drives the ROI story</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="59" t="inlineStr">
+        <is>
+          <t>Customer LTV</t>
+        </is>
+      </c>
+      <c r="C9" s="60" t="inlineStr">
+        <is>
+          <t>$15,340</t>
+        </is>
+      </c>
+      <c r="D9" s="60" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E9" s="60" t="inlineStr">
+        <is>
+          <t>$1,800-5,200</t>
+        </is>
+      </c>
+      <c r="F9" s="60" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>HVAC LTV is exceptional</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Net margin</t>
+        </is>
+      </c>
+      <c r="C10" s="58" t="inlineStr">
+        <is>
+          <t>8-12%</t>
+        </is>
+      </c>
+      <c r="D10" s="58" t="inlineStr">
+        <is>
+          <t>2-8% median / 20-35% leaders</t>
+        </is>
+      </c>
+      <c r="E10" s="58" t="inlineStr">
+        <is>
+          <t>est. 15-25%</t>
+        </is>
+      </c>
+      <c r="F10" s="58" t="inlineStr">
+        <is>
+          <t>12.5-30%</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Plumbing is bimodal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="59" t="inlineStr">
+        <is>
+          <t>Monthly profit</t>
+        </is>
+      </c>
+      <c r="C11" s="60" t="inlineStr">
+        <is>
+          <t>$5K-15K</t>
+        </is>
+      </c>
+      <c r="D11" s="60" t="inlineStr">
+        <is>
+          <t>$2K-8.5K / $21K-37K</t>
+        </is>
+      </c>
+      <c r="E11" s="60" t="inlineStr">
+        <is>
+          <t>$23K-39K</t>
+        </is>
+      </c>
+      <c r="F11" s="60" t="inlineStr">
+        <is>
+          <t>$2.1K-4.2K</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>This is the affordability line</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>$2,000 retainer as % profit</t>
+        </is>
+      </c>
+      <c r="C12" s="58" t="inlineStr">
+        <is>
+          <t>13-40%</t>
+        </is>
+      </c>
+      <c r="D12" s="58" t="inlineStr">
+        <is>
+          <t>24-94% / 5-10%</t>
+        </is>
+      </c>
+      <c r="E12" s="58" t="inlineStr">
+        <is>
+          <t>5-9%</t>
+        </is>
+      </c>
+      <c r="F12" s="58" t="inlineStr">
+        <is>
+          <t>48-95%</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Under 15% is comfortable</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="59" t="inlineStr">
+        <is>
+          <t>US business count</t>
+        </is>
+      </c>
+      <c r="C13" s="60" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D13" s="60" t="inlineStr">
+        <is>
+          <t>113,347</t>
+        </is>
+      </c>
+      <c r="E13" s="60" t="inlineStr">
+        <is>
+          <t>10,000+ locations</t>
+        </is>
+      </c>
+      <c r="F13" s="60" t="inlineStr">
+        <is>
+          <t>16,879 incl. car wash</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>TAM check</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>AFFORDABILITY VERDICT</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>NEEDS ROI CASE</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>LEADERS ONLY</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>COMFORTABLE</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="inlineStr">
+        <is>
+          <t>CANNOT AFFORD</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Retainer vs monthly profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Q4 SEASONAL FIT</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t>POOR - off season</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>You sell Aug-Nov. Timing is a filter, not a footnote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ENTRY PLAYBOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Lead product</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Top 3 pain signals</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Expected ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>Voice AI receptionist</t>
+        </is>
+      </c>
+      <c r="D19" s="62" t="n"/>
+      <c r="E19" s="38" t="inlineStr">
+        <is>
+          <t>1. Main line rings to mobile or voicemail in posted hours  2. Receptionist posting live 30+ days  3. Reviews citing 'never called back'</t>
+        </is>
+      </c>
+      <c r="F19" s="62" t="n"/>
+      <c r="G19" s="61" t="inlineStr">
+        <is>
+          <t>$1,500-2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+      <c r="C20" s="61" t="inlineStr">
+        <is>
+          <t>Voice AI, after-hours wedge</t>
+        </is>
+      </c>
+      <c r="D20" s="62" t="n"/>
+      <c r="E20" s="38" t="inlineStr">
+        <is>
+          <t>1. Advertises 24/7 but off-hours call fails  2. Answering service in use (price anchor)  3. Paid ads running to a slow-response number</t>
+        </is>
+      </c>
+      <c r="F20" s="62" t="n"/>
+      <c r="G20" s="61" t="inlineStr">
+        <is>
+          <t>$1,500-2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Med Spa</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="inlineStr">
+        <is>
+          <t>SMS reactivation. NOT voice</t>
+        </is>
+      </c>
+      <c r="D21" s="62" t="n"/>
+      <c r="E21" s="38" t="inlineStr">
+        <is>
+          <t>1. On Boulevard (weak attribution + LTV reporting)  2. Review count far exceeds recent velocity  3. No email or SMS marketing footprint</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="61" t="inlineStr">
+        <is>
+          <t>$2,000-3,000 single / $4,000-6,000 group</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Auto Detailing</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>DEPRIORITISE this quarter</t>
+        </is>
+      </c>
+      <c r="D22" s="62" t="n"/>
+      <c r="E22" s="64" t="inlineStr">
+        <is>
+          <t>Fails on affordability AND Q4 seasonality. Keep the accounts and products; revisit in spring.</t>
+        </is>
+      </c>
+      <c r="F22" s="62" t="n"/>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>HVAC: each missed call costs $350+; 5 missed calls a week is $91,000 a year. Published in their own trade press. Your single best sales asset.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E21:F21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Up-Market vs Fast-Market vs Barbell</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Same gap to close. Three routes. The barbell hedges the 30 November deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Up-market</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Fast-market</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BARBELL</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Blended ACV</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>$4,000</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>$2,250</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>$2,735</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Price is the biggest lever on funnel volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="59" t="inlineStr">
+        <is>
+          <t>Customers needed</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Each one consumes delivery capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Typical cycle</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>30-90 days</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>14-45 days</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Cycle, not revenue, is the binding constraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="59" t="inlineStr">
+        <is>
+          <t>Cohorts before 30 Nov</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>~2</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>~4</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>2 slow + 4 fast</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>More shots on goal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Close rate band</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>20-28%</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>25-35%</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Smaller simpler decisions close better</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="59" t="inlineStr">
+        <is>
+          <t>Dials/month, outbound</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>~800</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>~600</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Two callers at 40/day sustainable</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Main risk</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Deals slip past 30 Nov</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Volume strain on 2 callers</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>The barbell fails more gracefully</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>THE BARBELL, COMPOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>ACV/mo</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>MRR</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Who</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Group tier</t>
+        </is>
+      </c>
+      <c r="C17" s="21">
+        <f>Assumptions!C17</f>
+        <v/>
+      </c>
+      <c r="D17" s="65">
+        <f>Assumptions!C18</f>
+        <v/>
+      </c>
+      <c r="E17" s="14">
+        <f>C17*D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>3-8 location med spa groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Fast tier</t>
+        </is>
+      </c>
+      <c r="C18" s="21">
+        <f>Assumptions!C19</f>
+        <v/>
+      </c>
+      <c r="D18" s="65">
+        <f>Assumptions!C20</f>
+        <v/>
+      </c>
+      <c r="E18" s="14">
+        <f>C18*D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Single-location HVAC, plumbing LEADERS, med spa $1.5M+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>Total new MRR</t>
+        </is>
+      </c>
+      <c r="C19" s="17">
+        <f>SUM(C17:C18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="9">
+        <f>SUM(E17:E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Plus current MRR</t>
+        </is>
+      </c>
+      <c r="E20" s="65">
+        <f>Assumptions!C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>DECEMBER COLLECTED</t>
+        </is>
+      </c>
+      <c r="E21" s="66">
+        <f>E19+E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>WHAT MAKES THE FAST TIER ACTUALLY FAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Lowering price does NOT shorten the cycle on its own. Engineer these or you get a small deal on a long cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C25" s="57" t="inlineStr">
+        <is>
+          <t>Month-to-month. No annual contract. Removes the biggest deliberation trigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C26" s="57" t="inlineStr">
+        <is>
+          <t>One decision maker, always. Filter hard on owner-operator markers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C27" s="57" t="inlineStr">
+        <is>
+          <t>Runs inside their existing software. No migration means no IT conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C28" s="57" t="inlineStr">
+        <is>
+          <t>Published pricing. Negotiation adds weeks; a firm number closes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C29" s="57" t="inlineStr">
+        <is>
+          <t>Two calls maximum: diagnosis then proposal. A third call means it is a Group deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C30" s="57" t="inlineStr">
+        <is>
+          <t>Time-to-value under 14 days. They test cheaply instead of deliberating expensively.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>